--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137172724</v>
       </c>
       <c r="B9" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -835,11 +835,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandstorp, Ulrika kyrka, Ög</t>
@@ -1176,11 +1172,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandstorp, Ulrika kyrka, Ög</t>
@@ -1293,11 +1285,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rösätter, Ög</t>
@@ -1414,11 +1402,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rösätter, Ög</t>
@@ -1531,11 +1515,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rösätter, Ög</t>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137172917</v>
       </c>
       <c r="B4" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137172946</v>
       </c>
       <c r="B5" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137172724</v>
       </c>
       <c r="B9" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40284-2026 artfynd.xlsx
+++ b/artfynd/A 40284-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137173011</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137171903</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>137171827</v>
       </c>
       <c r="B6" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137172355</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>137172357</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137172167</v>
       </c>
       <c r="B10" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>137173042</v>
       </c>
       <c r="B11" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
